--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.93418836035741</v>
+        <v>4.376805608558079</v>
       </c>
       <c r="D2" t="n">
-        <v>26.59815654366052</v>
+        <v>4.322200438344835</v>
       </c>
       <c r="E2" t="n">
-        <v>9.614928454228343</v>
+        <v>1.562425873812106</v>
       </c>
       <c r="F2" t="n">
-        <v>8.274686145610159</v>
+        <v>1.344636498661651</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.85973550060874</v>
+        <v>6.152207018848921</v>
       </c>
       <c r="D3" t="n">
-        <v>30.63565503967703</v>
+        <v>4.978293943947518</v>
       </c>
       <c r="E3" t="n">
-        <v>9.614928454228343</v>
+        <v>1.562425873812106</v>
       </c>
       <c r="F3" t="n">
-        <v>8.274686145610159</v>
+        <v>1.344636498661651</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.86570563722307</v>
+        <v>5.828177166048749</v>
       </c>
       <c r="D4" t="n">
-        <v>35.75320775048699</v>
+        <v>5.809896259454137</v>
       </c>
       <c r="E4" t="n">
-        <v>9.614928454228343</v>
+        <v>1.562425873812106</v>
       </c>
       <c r="F4" t="n">
-        <v>8.274686145610159</v>
+        <v>1.344636498661651</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.39602641593473</v>
+        <v>5.751854292589393</v>
       </c>
       <c r="D5" t="n">
-        <v>20.29738009624426</v>
+        <v>3.298324265639693</v>
       </c>
       <c r="E5" t="n">
-        <v>9.614928454228343</v>
+        <v>1.562425873812106</v>
       </c>
       <c r="F5" t="n">
-        <v>8.274686145610159</v>
+        <v>1.344636498661651</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>11.87847800037252</v>
+        <v>1.930252675060535</v>
       </c>
       <c r="D6" t="n">
-        <v>11.95000688287316</v>
+        <v>1.941876118466889</v>
       </c>
       <c r="E6" t="n">
-        <v>9.614928454228343</v>
+        <v>1.562425873812106</v>
       </c>
       <c r="F6" t="n">
-        <v>8.274686145610159</v>
+        <v>1.344636498661651</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
